--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -137,10 +137,10 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3475,7 +3475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3711,7 +3711,7 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Rent-roll tie-outs</t>
+          <t>Across the two documents: statement vs rent roll</t>
         </is>
       </c>
       <c r="B16" s="16" t="n"/>
@@ -3723,22 +3723,22 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Our calc</t>
+          <t>Statement</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Rent roll</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -3748,426 +3748,361 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Basis / why not</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Total units</t>
+          <t>Gross Potential Rent vs the roll's market rent x 12</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>180</v>
+        <v>3905933.43</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>0</v>
+        <v>4107606</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>-0.04909735013533437</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>Unit count after de-duplicating rows for units listed twice mid-turnover.</t>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>statement GPR, twelve months; roll market rent, every unit, x 12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Total square feet</t>
+          <t>Total Revenue vs the roll's in-place rent x 12</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>190440</v>
+        <v>3814903.84</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>178020</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>12420</v>
+        <v>3813336</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>0.0004111465656317332</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>This project's own addition — the operator's rent-roll skill has no square-footage tie-out. It earns its place because square footage is what the de-duplication is checked against: dropping the wrong duplicate row changes the total.</t>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>statement total revenue; roll in-place rent, occupied units, x 12</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Occupied units (physical)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>177</v>
-      </c>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>NOT CHECKED</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>The source states no per-status unit table, so physical occupancy cannot be tied to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="n">
-        <v>0.9833333333333333</v>
-      </c>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>NOT CHECKED</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>PHYSICAL occupancy: 177 of 180 units. Residents on notice count as occupied; down, model and employee units do not. Economic occupancy is a different number and is not this one.</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Figures, not formulas — the roll is another workbook. A gap inside 10% reads OK; wider reads REVIEW; a side that is not there reads NOT CHECKED with the reason.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Market rent (monthly total)</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>342300.5</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>342300.5</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>Validates row COMPLETENESS — 180 units counted once each, none dropped or double-counted. It does NOT validate which row was kept on a duplicate: all 3 readable turnover pair(s) carry the same market rent on both rows, so this total is identical under either de-duplication rule while in-place rent is not. The row CHOICE is checked separately below.</t>
-        </is>
-      </c>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Rent-roll tie-outs</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Duplicate rows: kept the in-place lease</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>3 unit(s) listed twice; every one where an in-place row was available retained it (1 had none — D-NOCUR, where the alternative row carries no status and no rent, so keeping the other is correct). Keeping the other row instead would move in-place rent by $1,599/mo ($19,188/yr) — which the market-rent tie-out above cannot see.</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Our calc</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>Unit count after de-duplicating rows for units listed twice mid-turnover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Total square feet</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>190440</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>178020</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>12420</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>This project's own addition — the operator's rent-roll skill has no square-footage tie-out. It earns its place because square footage is what the de-duplication is checked against: dropping the wrong duplicate row changes the total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Occupied units (physical)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>177</v>
+      </c>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>The source states no per-status unit table, so physical occupancy cannot be tied to it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="n">
+        <v>0.9833333333333333</v>
+      </c>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>NOT CHECKED</t>
+        </is>
+      </c>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>PHYSICAL occupancy: 177 of 180 units. Residents on notice count as occupied; down, model and employee units do not. Economic occupancy is a different number and is not this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Market rent (monthly total)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>342300.5</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>342300.5</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>Validates row COMPLETENESS — 180 units counted once each, none dropped or double-counted. It does NOT validate which row was kept on a duplicate: all 3 readable turnover pair(s) carry the same market rent on both rows, so this total is identical under either de-duplication rule while in-place rent is not. The row CHOICE is checked separately below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Duplicate rows: kept the in-place lease</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>3 unit(s) listed twice; every one where an in-place row was available retained it (1 had none — D-NOCUR, where the alternative row carries no status and no rent, so keeping the other is correct). Keeping the other row instead would move in-place rent by $1,599/mo ($19,188/yr) — which the market-rent tie-out above cannot see.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>Occupied units</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B30" s="6" t="n">
         <v>177</v>
       </c>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>The numerator above, stated separately so the ratio can be re-derived.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>3/6 tie-outs OK; 2 NOT CHECKED</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>A total the source export never printed reads NOT CHECKED and stays in the denominator above — excluding it would let a check that could not run flatter the ratio. Occupancy here is PHYSICAL: 177/180 units, physical. Down, model and employee units count as vacant.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Rent readback — 10 units, sampled reproducibly</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
+      <c r="F35" s="16" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Our in-place rent</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Source cell value</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Source locator</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>A1-123</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>1417</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>1417</v>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Rent Roll (source)!F26</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>A1-130</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>1438</v>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>1438</v>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Rent Roll (source)!F33</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>A2-108</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>1564</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>1564</v>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Rent Roll (source)!F45</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>B1-101</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>1831</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>1831</v>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Rent Roll (source)!F66</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>B1-103</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>1809</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>1809</v>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Rent Roll (source)!F68</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>B1-113</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="n">
-        <v>1734</v>
-      </c>
-      <c r="D36" s="6" t="n">
-        <v>1734</v>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Rent Roll (source)!F78</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>B1-126</t>
+          <t>A1-123</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>1799</v>
+        <v>1417</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>1799</v>
+        <v>1417</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F91</t>
+          <t>Rent Roll (source)!F26</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -4179,23 +4114,23 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>B2-123</t>
+          <t>A1-130</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1887</v>
+        <v>1438</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>1887</v>
+        <v>1438</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F130</t>
+          <t>Rent Roll (source)!F33</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -4207,23 +4142,23 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>C1-118</t>
+          <t>A2-108</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>2056</v>
+        <v>1564</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>2056</v>
+        <v>1564</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F161</t>
+          <t>Rent Roll (source)!F45</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -4235,23 +4170,23 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Cypress-106</t>
+          <t>B1-101</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Cypress TH</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>2343</v>
+        <v>1831</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>2343</v>
+        <v>1831</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Rent Roll (source)!F175</t>
+          <t>Rent Roll (source)!F66</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -4260,263 +4195,431 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>B1-103</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>1809</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>1809</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F68</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>10 of 10 match within $0.50. Sample seeded from the roll's as-of date (2026-06-30|180), so the same roll always checks the same units and a reviewer re-running this sees these rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>Both sides of the readback read the same rent column, so it validates TRANSCRIPTION — that the number was carried across correctly — and cannot detect the wrong column having been chosen in the first place. The column choice is evidenced in the audit trail instead.</t>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>B1-113</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>1734</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>1734</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F78</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>B1-126</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>1799</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F91</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>B2-123</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>1887</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>1887</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F130</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>Pricing and cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>C1-118</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>2056</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>2056</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F161</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Price per unit</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="n">
-        <v>215000</v>
-      </c>
-      <c r="C46" s="20" t="inlineStr">
-        <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Unit count</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>180</v>
+          <t>Cypress-106</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Cypress TH</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>2343</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>2343</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Rent Roll (source)!F175</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Total purchase price</t>
-        </is>
-      </c>
-      <c r="B48" s="6">
-        <f>B46*B47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B50" s="6">
-        <f>'P&amp;L Summary'!B16</f>
-        <v/>
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>10 of 10 match within $0.50. Sample seeded from the roll's as-of date (2026-06-30|180), so the same roll always checks the same units and a reviewer re-running this sees these rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>Both sides of the readback read the same rent column, so it validates TRANSCRIPTION — that the number was carried across correctly — and cannot detect the wrong column having been chosen in the first place. The column choice is evidenced in the audit trail instead.</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>T-12 operating expenses</t>
-        </is>
-      </c>
-      <c r="B51" s="6">
-        <f>'P&amp;L Summary'!B29</f>
-        <v/>
-      </c>
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Pricing and cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="n"/>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="n"/>
+      <c r="E51" s="16" t="n"/>
+      <c r="F51" s="16" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>T-12 net operating income</t>
-        </is>
-      </c>
-      <c r="B52" s="6">
-        <f>'P&amp;L Summary'!B30</f>
-        <v/>
+          <t>Price per unit</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>215000</v>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>T-12 cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B53" s="21">
-        <f>IFERROR(B52/B48,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>T-3 annualized revenue</t>
-        </is>
-      </c>
-      <c r="B55" s="6">
-        <f>'P&amp;L Summary'!C16</f>
+          <t>Unit count</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Total purchase price</t>
+        </is>
+      </c>
+      <c r="B54" s="6">
+        <f>B52*B53</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized operating expenses</t>
+          <t>T-12 revenue</t>
         </is>
       </c>
       <c r="B56" s="6">
-        <f>'P&amp;L Summary'!C29</f>
+        <f>'P&amp;L Summary'!B16</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized net operating income</t>
+          <t>T-12 operating expenses</t>
         </is>
       </c>
       <c r="B57" s="6">
-        <f>'P&amp;L Summary'!C30</f>
+        <f>'P&amp;L Summary'!B29</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B58" s="21">
-        <f>IFERROR(B57/B48,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>Broker pro forma revenue</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="n">
-        <v>4051427.88</v>
-      </c>
-      <c r="C60" s="20" t="inlineStr">
-        <is>
-          <t>Kept in its own block; never merged into the T-12.</t>
-        </is>
+          <t>T-12 net operating income</t>
+        </is>
+      </c>
+      <c r="B58" s="6">
+        <f>'P&amp;L Summary'!B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>T-12 cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B59" s="21">
+        <f>IFERROR(B58/B54,"")</f>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma operating expenses</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="n">
-        <v>1718834.16</v>
+          <t>T-3 annualized revenue</t>
+        </is>
+      </c>
+      <c r="B61" s="6">
+        <f>'P&amp;L Summary'!C16</f>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma net operating income</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="n">
-        <v>2332593.72</v>
+          <t>T-3 annualized operating expenses</t>
+        </is>
+      </c>
+      <c r="B62" s="6">
+        <f>'P&amp;L Summary'!C29</f>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Broker pro forma cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B63" s="21">
-        <f>IFERROR(B62/B48,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="16" t="inlineStr">
-        <is>
-          <t>Revenue trend</t>
-        </is>
-      </c>
-      <c r="B65" s="16" t="n"/>
-      <c r="C65" s="16" t="n"/>
-      <c r="D65" s="16" t="n"/>
-      <c r="E65" s="16" t="n"/>
-      <c r="F65" s="16" t="n"/>
+          <t>T-3 annualized net operating income</t>
+        </is>
+      </c>
+      <c r="B63" s="6">
+        <f>'P&amp;L Summary'!C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>T-3 annualized cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B64" s="21">
+        <f>IFERROR(B63/B54,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B66" s="6">
-        <f>'P&amp;L Summary'!B16</f>
-        <v/>
+          <t>Broker pro forma revenue</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>4051427.88</v>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>Kept in its own block; never merged into the T-12.</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>T-6 revenue (annualized)</t>
-        </is>
-      </c>
-      <c r="B67" s="6">
-        <f>SUM('T-12 Data'!I39:N39)*2</f>
-        <v/>
-      </c>
-      <c r="C67" s="20" t="inlineStr">
-        <is>
-          <t>Trailing six months times two, off the T-12 Data tab's computed revenue row.</t>
-        </is>
+          <t>Broker pro forma operating expenses</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>1718834.16</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>T-3 revenue (annualized)</t>
-        </is>
-      </c>
-      <c r="B68" s="6">
-        <f>'P&amp;L Summary'!C16</f>
-        <v/>
+          <t>Broker pro forma net operating income</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>2332593.72</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
+          <t>Broker pro forma cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B69" s="21">
+        <f>IFERROR(B68/B54,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>Revenue trend</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="n"/>
+      <c r="C71" s="16" t="n"/>
+      <c r="D71" s="16" t="n"/>
+      <c r="E71" s="16" t="n"/>
+      <c r="F71" s="16" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>T-12 revenue</t>
+        </is>
+      </c>
+      <c r="B72" s="6">
+        <f>'P&amp;L Summary'!B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>T-6 revenue (annualized)</t>
+        </is>
+      </c>
+      <c r="B73" s="6">
+        <f>SUM('T-12 Data'!I39:N39)*2</f>
+        <v/>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>Trailing six months times two, off the T-12 Data tab's computed revenue row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>T-3 revenue (annualized)</t>
+        </is>
+      </c>
+      <c r="B74" s="6">
+        <f>'P&amp;L Summary'!C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
           <t>T-3 versus T-12</t>
         </is>
       </c>
-      <c r="B69" s="19">
-        <f>IFERROR(B68/B50-1,"")</f>
-        <v/>
-      </c>
-      <c r="C69" s="20" t="inlineStr">
+      <c r="B75" s="18">
+        <f>IFERROR(B74/B56-1,"")</f>
+        <v/>
+      </c>
+      <c r="C75" s="20" t="inlineStr">
         <is>
           <t>Positive means the trailing three months are running ahead of the year.</t>
         </is>
@@ -4662,7 +4765,7 @@
         </is>
       </c>
       <c r="F9" s="17" t="n"/>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>Illustrative. Inside the band a per-unit sale price occupies.</t>
         </is>
@@ -4728,7 +4831,7 @@
         </is>
       </c>
       <c r="F11" s="17" t="n"/>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>Twelve consecutive month-end columns; direction detected from the labels.</t>
         </is>
@@ -4761,7 +4864,7 @@
         </is>
       </c>
       <c r="F12" s="17" t="n"/>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>The statement's own printed subtotals, kept for the cross-tie.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9014,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -10140,7 +10140,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,10 +137,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2056,7 +2057,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Revenue Adjustments</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C31" s="6" t="n">
@@ -2168,7 +2169,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Revenue Adjustments</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C33" s="6" t="n">
@@ -4016,7 +4017,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>General and Administrative</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
@@ -4072,7 +4073,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>General and Administrative</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
@@ -8014,7 +8015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8667,7 +8668,7 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>Other Income — top 4 plus rest</t>
+          <t>Other Income — top 5 plus rest</t>
         </is>
       </c>
       <c r="B34" s="15" t="n"/>
@@ -8732,254 +8733,362 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>LATE CHARGES (3011)</t>
+          <t>RENTER'S INSURANCE EXPENSE (3176)</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>52406.47</v>
+        <v>-55891.32</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>37520.16</v>
+        <v>-57108.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>All other other income (16 lines)</t>
+          <t>LATE CHARGES (3011)</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>207144.18</v>
+        <v>52406.47</v>
       </c>
       <c r="C40" s="6" t="n">
+        <v>37520.16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>All other other income (17 lines)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>200733</v>
+      </c>
+      <c r="C41" s="6" t="n">
         <v>196518.6</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Total other income</t>
         </is>
       </c>
-      <c r="B41" s="13">
+      <c r="B42" s="13">
         <f>'P&amp;L Summary'!B14</f>
         <v/>
       </c>
-      <c r="C41" s="13">
+      <c r="C42" s="13">
         <f>'P&amp;L Summary'!C14</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>Utility Reimbursements — top 4 plus rest</t>
         </is>
       </c>
-      <c r="B43" s="15" t="n"/>
-      <c r="C43" s="15" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="15" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>T-12</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>T-3 annualized</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>WATER/SEWER REIMBURSEMENT (3186)</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="n">
-        <v>209955.79</v>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>202017.76</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>VALET TRASH REIMBURSEMENTS (3001)</t>
+          <t>WATER/SEWER REIMBURSEMENT (3186)</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>92098.19</v>
+        <v>209955.79</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>102302.8</v>
+        <v>202017.76</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TRASH REIMBURSEMENT (3187)</t>
+          <t>VALET TRASH REIMBURSEMENTS (3001)</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>48980.96</v>
+        <v>92098.19</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>40944.64</v>
+        <v>102302.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>UTILITY FEE REIMBURSEMENT (3183)</t>
+          <t>TRASH REIMBURSEMENT (3187)</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>14581.28</v>
+        <v>48980.96</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>14432.88</v>
+        <v>40944.64</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
+          <t>UTILITY FEE REIMBURSEMENT (3183)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>14581.28</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>14432.88</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
           <t>All other utility reimbursements (1 lines)</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B50" s="6" t="n">
         <v>6318.52</v>
       </c>
-      <c r="C49" s="6" t="n">
+      <c r="C50" s="6" t="n">
         <v>3798.56</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Total utility reimbursements</t>
         </is>
       </c>
-      <c r="B50" s="13">
+      <c r="B51" s="13">
         <f>'P&amp;L Summary'!B13</f>
         <v/>
       </c>
-      <c r="C50" s="13">
+      <c r="C51" s="13">
         <f>'P&amp;L Summary'!C13</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Utilities — top 4 plus rest</t>
         </is>
       </c>
-      <c r="B52" s="15" t="n"/>
-      <c r="C52" s="15" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="15" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>T-12</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>T-3 annualized</t>
         </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>WATER (7060)</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="n">
-        <v>102297.25</v>
-      </c>
-      <c r="C54" s="6" t="n">
-        <v>104995.64</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>SEWAGE (7070)</t>
+          <t>WATER (7060)</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>84050.12</v>
+        <v>102297.25</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>85693.79999999999</v>
+        <v>104995.64</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>TRASH REMOVAL (7025)</t>
+          <t>SEWAGE (7070)</t>
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>57099.47</v>
+        <v>84050.12</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>64295.64</v>
+        <v>85693.79999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>VALET TRASH (7026)</t>
+          <t>TRASH REMOVAL (7025)</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>37188.33</v>
+        <v>57099.47</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>36140.28</v>
+        <v>64295.64</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>All other utilities (7 lines)</t>
+          <t>VALET TRASH (7026)</t>
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>70098.53999999999</v>
+        <v>37188.33</v>
       </c>
       <c r="C58" s="6" t="n">
-        <v>68465.39999999999</v>
+        <v>36140.28</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>All other utilities (5 lines)</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>56529.97</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>51636.28</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>Total utilities</t>
         </is>
       </c>
-      <c r="B59" s="13">
+      <c r="B60" s="13">
         <f>'P&amp;L Summary'!B27</f>
         <v/>
       </c>
-      <c r="C59" s="13">
+      <c r="C60" s="13">
         <f>'P&amp;L Summary'!C27</f>
         <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>Trailing T-3 annualized revenue</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="15" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>T-3 annualized revenue</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>6022368.64</v>
+      </c>
+      <c r="C64" s="17" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>6022883.76</v>
+      </c>
+      <c r="C65" s="17" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>6075786.08</v>
+      </c>
+      <c r="C66" s="17" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>6144708.68</v>
+      </c>
+      <c r="C67" s="17" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>6100665.88</v>
+      </c>
+      <c r="C68" s="17" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>6228784.32</v>
+      </c>
+      <c r="C69" s="17" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Each figure is that month plus the two before it, times four — the trend the T-3 cap rate sits at the end of. Fewer than eight months of statement give fewer figures, never a padded zero.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8993,7 +9102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -9231,7 +9340,7 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Across the two documents: statement vs rent roll</t>
+          <t>Statement sanity checks</t>
         </is>
       </c>
       <c r="B16" s="15" t="n"/>
@@ -9243,865 +9352,1289 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Statement</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Rent roll</t>
+          <t>Lines named</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Basis / why not</t>
-        </is>
-      </c>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Gross Potential Rent vs the roll's market rent x 12</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>5827603.6</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>5651856</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>0.0310955551592255</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
+          <t>Contra-revenue categories net negative</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>statement GPR, twelve months; roll market rent, every unit, x 12</t>
-        </is>
-      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Every contra-revenue category (Vacancy, Concessions, Non-Revenue Units, Delinquency) nets negative, as it must.</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Total Revenue vs the roll's in-place rent x 12</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>6166659.01</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>5472456</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>0.1268540139929859</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>statement total revenue; roll in-place rent, occupied units, x 12</t>
-        </is>
-      </c>
+          <t>Total operating expenses positive</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Total operating expenses are $2,054,908 — positive, as an expense total must be.</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Figures, not formulas — the roll is another workbook. A gap inside 10% reads OK; wider reads REVIEW; a side that is not there reads NOT CHECKED with the reason.</t>
-        </is>
-      </c>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>No recovery lines inside expense buckets</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>No negative line inside an expense category carries a recovery word (rebill, reimburse, recover, recapture).</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>No subtotal row counted with its members</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>No categorised row named like a subtotal (|value| ≥ $500) equals the sum of one to three rows within 25 lines of it.</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Rent-roll tie-outs</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Our calc</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>A REVIEW here is a fact about how the statement is printed, flagged for a reader to resolve; the P&amp;L above is the statement as categorised, unflipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Across the two documents: statement vs rent roll</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Statement</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Rent roll</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Total units</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>334</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>334</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>Unit count after de-duplicating rows for units listed twice mid-turnover.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Total square feet</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>285882</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>285882</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>This project's own addition — the operator's rent-roll skill has no square-footage tie-out. It earns its place because square footage is what the de-duplication is checked against: dropping the wrong duplicate row changes the total.</t>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Basis / why not</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Occupied units (physical)</t>
+          <t>Gross Potential Rent vs the roll's market rent x 12</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>313</v>
+        <v>5827603.6</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>313</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>5651856</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>0.0310955551592255</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>Against the source's own status buckets: Occupied + Notice Available + Notice Rented. A resident on notice has not moved out, so the source's 'Occupied' bucket alone is a LEASING status, not physical occupancy.</t>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>statement GPR, twelve months; roll market rent, every unit, x 12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="n">
-        <v>0.937125748502994</v>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>0.937125748502994</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>0</v>
+          <t>Total Revenue vs the roll's in-place rent x 12</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>6166659.01</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>5472456</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>0.1268540139929859</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>statement total revenue; roll in-place rent, occupied units, x 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Figures, not formulas — the roll is another workbook. A gap inside 10% reads OK; wider reads REVIEW; a side that is not there reads NOT CHECKED with the reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>Units off by</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>Market rent off by</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Unit count (tolerance 0) and the export's stated market-rent total (tolerance $1), plus every duplicate row retaining the in-place lease and no rent-readback mismatch. FAIL on any; NOT CHECKED when the export states no count or no total to tie to; PASS only when everything ran and tied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Rent-roll tie-outs</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Our calc</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Total units</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>334</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>334</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>PHYSICAL occupancy: 313 of 334 units. Residents on notice count as occupied; down, model and employee units do not. Economic occupancy is a different number and is not this one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Market rent (monthly total)</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>470988</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>448550</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>22438</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>Validates row COMPLETENESS — 334 units counted once each, none dropped or double-counted. It does NOT validate which row was kept on a duplicate: all 6 readable turnover pair(s) carry the same market rent on both rows, so this total is identical under either de-duplication rule while in-place rent is not. The row CHOICE is checked separately below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Duplicate rows: kept the in-place lease</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>6 unit(s) listed twice; every one where an in-place row was available retained it (1 had none — 2107, where the alternative row carries no status and no rent, so keeping the other is correct). Keeping the other row instead would move in-place rent by $4,823/mo ($57,876/yr) — which the market-rent tie-out above cannot see.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Occupied units</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>313</v>
-      </c>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>The numerator above, stated separately so the ratio can be re-derived.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>5/6 tie-outs OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>A total the source export never printed reads NOT CHECKED and stays in the denominator above — excluding it would let a check that could not run flatter the ratio. Occupancy here is PHYSICAL: 313/334 units, physical. Down, model and employee units count as vacant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>Rent readback — 10 units, sampled reproducibly</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="n"/>
-      <c r="F35" s="15" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Plan</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Our in-place rent</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Source cell value</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Source locator</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>Unit count after de-duplicating rows for units listed twice mid-turnover.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>2X1R</t>
-        </is>
+          <t>Total square feet</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>285882</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>1388</v>
+        <v>285882</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>1388</v>
+        <v>0</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>HG_RMOROLLE!N25</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>This project's own addition — the operator's rent-roll skill has no square-footage tie-out. It earns its place because square footage is what the de-duplication is checked against: dropping the wrong duplicate row changes the total.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>1027</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>2X2R</t>
-        </is>
+          <t>Occupied units (physical)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>313</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1307</v>
+        <v>313</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>1307</v>
+        <v>0</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>HG_RMOROLLE!N30</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>Against the source's own status buckets: Occupied + Notice Available + Notice Rented. A resident on notice has not moved out, so the source's 'Occupied' bucket alone is a LEASING status, not physical occupancy.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>1X1R</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>1653</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>1653</v>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>0.937125748502994</v>
+      </c>
+      <c r="C39" s="19" t="n">
+        <v>0.937125748502994</v>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>0</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>HG_RMOROLLE!N33</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>PHYSICAL occupancy: 313 of 334 units. Residents on notice count as occupied; down, model and employee units do not. Economic occupancy is a different number and is not this one.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>1041</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>1X1</t>
-        </is>
+          <t>Market rent (monthly total)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>470988</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>1224</v>
+        <v>470988</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>1224</v>
+        <v>0</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>HG_RMOROLLE!N44</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>Validates row COMPLETENESS — 334 units counted once each, none dropped or double-counted. It does NOT validate which row was kept on a duplicate: all 6 readable turnover pair(s) carry the same market rent on both rows, so this total is identical under either de-duplication rule while in-place rent is not. The row CHOICE is checked separately below.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>1079</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>3X2AR</t>
-        </is>
+          <t>In-place rent (monthly total)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>457414</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>1998</v>
+        <v>488975</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>1998</v>
+        <v>-31561</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>HG_RMOROLLE!N84</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>Shown for the reader, not scored: the export's current-rent total is its per-status summary, which carries a rent on model, unrentable and vacant units; in-place rent is occupied units only. The gate's rent half is the market-rent total above, which the export states on the same per-unit basis.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>2X2R</t>
-        </is>
+          <t>Duplicate rows: kept the in-place lease</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>1470</v>
+        <v>6</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>1470</v>
+        <v>0</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>HG_RMOROLLE!N105</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
           <t>OK</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>6 unit(s) listed twice; every one where an in-place row was available retained it (1 had none — 2107, where the alternative row carries no status and no rent, so keeping the other is correct). Keeping the other row instead would move in-place rent by $4,823/mo ($57,876/yr) — which the market-rent tie-out above cannot see.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>1144</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>1X1R</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>1351</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>1351</v>
-      </c>
+          <t>Occupied units</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>313</v>
+      </c>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>HG_RMOROLLE!N150</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>1X1R</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>1181</v>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>1181</v>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>HG_RMOROLLE!N165</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>The numerator above, stated separately so the ratio can be re-derived.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>1167</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>2X2</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>1748</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>1748</v>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>HG_RMOROLLE!N174</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>6/6 tie-outs OK</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>2X2</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="n">
-        <v>1496</v>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>1496</v>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>HG_RMOROLLE!N188</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>A total the source export never printed reads NOT CHECKED and stays in the denominator above — excluding it would let a check that could not run flatter the ratio. Occupancy here is PHYSICAL: 313/334 units, physical. Down, model and employee units count as vacant.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>10 of 10 match within $0.50. Sample seeded from the roll's as-of date (2026-08-31|334), so the same roll always checks the same units and a reviewer re-running this sees these rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>Both sides of the readback read the same rent column, so it validates TRANSCRIPTION — that the number was carried across correctly — and cannot detect the wrong column having been chosen in the first place. The column choice is evidenced in the audit trail instead.</t>
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Duplicate rows — 6 unit(s) listed twice</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="n"/>
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="15" t="n"/>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="15" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Kept row</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Kept status</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Kept rent</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Rows not counted</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>1218</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>row 63: New, $0</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Kept the row whose lease status is the in-place one ('Current'); the other row is the incoming lease.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Pricing and cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="n"/>
-      <c r="C51" s="15" t="n"/>
-      <c r="D51" s="15" t="n"/>
-      <c r="E51" s="15" t="n"/>
-      <c r="F51" s="15" t="n"/>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>2397</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>row 81: New, $0</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Kept the row whose lease status is the in-place one ('Current'); the other row is the incoming lease.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Price per unit</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>215000</v>
-      </c>
-      <c r="C52" s="20" t="inlineStr">
-        <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        <v>110</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>2067</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>row 109: New, $1,606</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>Kept the row whose lease status is the in-place one ('Current'); the other row is the incoming lease.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Unit count</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>334</v>
+        <v>153</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>1555</v>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>row 152: New, $1,255</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>Kept the row whose lease status is the in-place one ('Current'); the other row is the incoming lease.</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Total purchase price</t>
-        </is>
-      </c>
-      <c r="B54" s="6">
-        <f>B52*B53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B56" s="6">
-        <f>'P&amp;L Summary'!B16</f>
-        <v/>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>197</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>1823</v>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>row 196: New, $1,376</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>Kept the row whose lease status is the in-place one ('Current'); the other row is the incoming lease.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>283</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>1376</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>row 284: no status, $0</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>No row carries the in-place status ('Current'); kept the row with a stated rent and a status, which is the lease in place on the as-of date.</t>
+        </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>T-12 operating expenses</t>
-        </is>
-      </c>
-      <c r="B57" s="6">
-        <f>'P&amp;L Summary'!B29</f>
-        <v/>
-      </c>
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Rent readback — 10 units, sampled reproducibly</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="n"/>
+      <c r="C57" s="15" t="n"/>
+      <c r="D57" s="15" t="n"/>
+      <c r="E57" s="15" t="n"/>
+      <c r="F57" s="15" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>T-12 net operating income</t>
-        </is>
-      </c>
-      <c r="B58" s="6">
-        <f>'P&amp;L Summary'!B30</f>
-        <v/>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Our in-place rent</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Source cell value</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Source locator</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>T-12 cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B59" s="21">
-        <f>IFERROR(B58/B54,"")</f>
-        <v/>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>2X1R</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>1388</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>1388</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>HG_RMOROLLE!N25</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>2X2R</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>1307</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>1307</v>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>HG_RMOROLLE!N30</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized revenue</t>
-        </is>
-      </c>
-      <c r="B61" s="6">
-        <f>'P&amp;L Summary'!C16</f>
-        <v/>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>1X1R</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>1653</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>HG_RMOROLLE!N33</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized operating expenses</t>
-        </is>
-      </c>
-      <c r="B62" s="6">
-        <f>'P&amp;L Summary'!C29</f>
-        <v/>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>1X1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>1224</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>HG_RMOROLLE!N44</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized net operating income</t>
-        </is>
-      </c>
-      <c r="B63" s="6">
-        <f>'P&amp;L Summary'!C30</f>
-        <v/>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>3X2AR</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>1998</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>HG_RMOROLLE!N84</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>T-3 annualized cap rate (illustrative)</t>
-        </is>
-      </c>
-      <c r="B64" s="21">
-        <f>IFERROR(B63/B54,"")</f>
-        <v/>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>2X2R</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>1470</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>1470</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>HG_RMOROLLE!N105</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>1144</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>1X1R</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>1351</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>1351</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>HG_RMOROLLE!N150</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="15" t="inlineStr">
-        <is>
-          <t>Revenue trend</t>
-        </is>
-      </c>
-      <c r="B66" s="15" t="n"/>
-      <c r="C66" s="15" t="n"/>
-      <c r="D66" s="15" t="n"/>
-      <c r="E66" s="15" t="n"/>
-      <c r="F66" s="15" t="n"/>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>1158</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>1X1R</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>1181</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>1181</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>HG_RMOROLLE!N165</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B67" s="6">
-        <f>'P&amp;L Summary'!B16</f>
-        <v/>
+          <t>1167</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>2X2</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>1748</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>1748</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>HG_RMOROLLE!N174</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>2X2</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>1496</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>1496</v>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>HG_RMOROLLE!N188</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>10 of 10 match within $0.50. Sample seeded from the roll's as-of date (2026-08-31|334), so the same roll always checks the same units and a reviewer re-running this sees these rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>Both sides of the readback read the same rent column, so it validates TRANSCRIPTION — that the number was carried across correctly — and cannot detect the wrong column having been chosen in the first place. The column choice is evidenced in the audit trail instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>Pricing and cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="n"/>
+      <c r="C73" s="15" t="n"/>
+      <c r="D73" s="15" t="n"/>
+      <c r="E73" s="15" t="n"/>
+      <c r="F73" s="15" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Price per unit</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>215000</v>
+      </c>
+      <c r="C74" s="21" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Unit count</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Total purchase price</t>
+        </is>
+      </c>
+      <c r="B76" s="6">
+        <f>B74*B75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>T-12 revenue</t>
+        </is>
+      </c>
+      <c r="B78" s="6">
+        <f>'P&amp;L Summary'!B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>T-12 operating expenses</t>
+        </is>
+      </c>
+      <c r="B79" s="6">
+        <f>'P&amp;L Summary'!B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>T-12 net operating income</t>
+        </is>
+      </c>
+      <c r="B80" s="6">
+        <f>'P&amp;L Summary'!B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>T-12 cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B81" s="22">
+        <f>IFERROR(B80/B76,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>T-3 annualized revenue</t>
+        </is>
+      </c>
+      <c r="B83" s="6">
+        <f>'P&amp;L Summary'!C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>T-3 annualized operating expenses</t>
+        </is>
+      </c>
+      <c r="B84" s="6">
+        <f>'P&amp;L Summary'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>T-3 annualized net operating income</t>
+        </is>
+      </c>
+      <c r="B85" s="6">
+        <f>'P&amp;L Summary'!C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>T-3 annualized cap rate (illustrative)</t>
+        </is>
+      </c>
+      <c r="B86" s="22">
+        <f>IFERROR(B85/B76,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>Revenue trend</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="n"/>
+      <c r="C88" s="15" t="n"/>
+      <c r="D88" s="15" t="n"/>
+      <c r="E88" s="15" t="n"/>
+      <c r="F88" s="15" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>T-12 revenue</t>
+        </is>
+      </c>
+      <c r="B89" s="6">
+        <f>'P&amp;L Summary'!B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
           <t>T-6 revenue (annualized)</t>
         </is>
       </c>
-      <c r="B68" s="6">
+      <c r="B90" s="6">
         <f>SUM('T-12 Data'!I137:N137)*2</f>
         <v/>
       </c>
-      <c r="C68" s="20" t="inlineStr">
+      <c r="C90" s="21" t="inlineStr">
         <is>
           <t>Trailing six months times two, off the T-12 Data tab's computed revenue row.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>T-3 revenue (annualized)</t>
         </is>
       </c>
-      <c r="B69" s="6">
+      <c r="B91" s="6">
         <f>'P&amp;L Summary'!C16</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>T-3 versus T-12</t>
         </is>
       </c>
-      <c r="B70" s="18">
-        <f>IFERROR(B69/B56-1,"")</f>
-        <v/>
-      </c>
-      <c r="C70" s="20" t="inlineStr">
+      <c r="B92" s="19">
+        <f>IFERROR(B91/B78-1,"")</f>
+        <v/>
+      </c>
+      <c r="C92" s="21" t="inlineStr">
         <is>
           <t>Positive means the trailing three months are running ahead of the year.</t>
         </is>
@@ -10221,7 +10754,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>pricing.price_per_unit</t>
         </is>
@@ -10247,14 +10780,14 @@
         </is>
       </c>
       <c r="F9" s="17" t="n"/>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>pricing.unit_count</t>
         </is>
@@ -10284,14 +10817,14 @@
           <t>summary.unit_count</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>t12.month_labels</t>
         </is>
@@ -10317,14 +10850,14 @@
         </is>
       </c>
       <c r="F11" s="17" t="n"/>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>Read from the uploaded statement.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>t12.source_subtotals</t>
         </is>
@@ -10350,10 +10883,10 @@
         </is>
       </c>
       <c r="F12" s="17" t="n"/>
-      <c r="G12" s="23" t="n"/>
+      <c r="G12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>t12.units</t>
         </is>
@@ -10379,7 +10912,7 @@
         </is>
       </c>
       <c r="F13" s="17" t="n"/>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>Read from the uploaded statement.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -8090,11 +8090,11 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A6,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A6)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A6,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C6" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A6,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A6)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A6,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D6" s="10">
@@ -8113,11 +8113,11 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A7,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A7)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A7,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C7" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A7,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A7)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A7,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D7" s="10">
@@ -8136,11 +8136,11 @@
         </is>
       </c>
       <c r="B8" s="13">
-        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A8)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A8,'T-12 Data'!$O$6:$O$135),B6+B7)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A8)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A8,'T-12 Data'!$O$6:$O$135),IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A6)+COUNTIF('T-12 Data'!$B$6:$B$135,$A7)&gt;0,IF(B6="",0,B6)+IF(B7="",0,B7),""))</f>
         <v/>
       </c>
       <c r="C8" s="13">
-        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A8)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A8,'T-12 Data'!$P$6:$P$135)*4,(C6+C7))</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A8)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A8,'T-12 Data'!$P$6:$P$135)*4,IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A6)+COUNTIF('T-12 Data'!$B$6:$B$135,$A7)&gt;0,IF(C6="",0,C6)+IF(C7="",0,C7),""))</f>
         <v/>
       </c>
       <c r="D8" s="13">
@@ -8159,11 +8159,11 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A9,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A9)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A9,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C9" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A9,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A9)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A9,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D9" s="10">
@@ -8182,11 +8182,11 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A10,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A10)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A10,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C10" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A10,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A10)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A10,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D10" s="10">
@@ -8205,11 +8205,11 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A11,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A11)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A11,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C11" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A11,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A11)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A11,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D11" s="10">
@@ -8228,11 +8228,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A12,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A12)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A12,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A12,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A12)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A12,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D12" s="10">
@@ -8251,11 +8251,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A13,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A13)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A13,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A13,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A13)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A13,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D13" s="10">
@@ -8274,11 +8274,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A14,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A14)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A14,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A14,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A14)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A14,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D14" s="10">
@@ -8297,11 +8297,11 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A15,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A15)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A15,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C15" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A15,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A15)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A15,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D15" s="10">
@@ -8343,11 +8343,11 @@
         </is>
       </c>
       <c r="B17" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A17,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A17)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A17,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C17" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A17,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A17)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A17,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D17" s="10">
@@ -8366,11 +8366,11 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A18,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A18)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A18,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A18,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A18)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A18,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D18" s="10">
@@ -8389,11 +8389,11 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A19,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A19)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A19,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A19,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A19)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A19,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D19" s="10">
@@ -8412,11 +8412,11 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A20,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A20)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A20,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A20,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A20)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A20,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D20" s="10">
@@ -8435,11 +8435,11 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A21,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A21)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A21,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A21,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A21)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A21,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D21" s="10">
@@ -8458,11 +8458,11 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A22,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A22)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A22,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A22,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A22)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A22,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D22" s="10">
@@ -8481,11 +8481,11 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A23,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A23)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A23,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A23,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A23)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A23,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D23" s="10">
@@ -8504,11 +8504,11 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A24,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A24)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A24,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A24,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A24)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A24,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D24" s="10">
@@ -8527,11 +8527,11 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A25,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A25)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A25,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A25,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A25)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A25,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D25" s="10">
@@ -8550,11 +8550,11 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A26,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A26)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A26,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A26,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A26)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A26,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D26" s="10">
@@ -8573,11 +8573,11 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A27,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A27)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A27,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A27,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A27)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A27,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D27" s="10">
@@ -8596,11 +8596,11 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A28,'T-12 Data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A28)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A28,'T-12 Data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>SUMIF('T-12 Data'!$B$6:$B$135,$A28,'T-12 Data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Data'!$B$6:$B$135,$A28)&gt;0,SUMIF('T-12 Data'!$B$6:$B$135,$A28,'T-12 Data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D28" s="10">
@@ -9202,7 +9202,7 @@
         <v>6166658.92</v>
       </c>
       <c r="D7" s="6">
-        <f>IFERROR(B7-C7,"")</f>
+        <f>IF(C7="","",IF(B7="",0,B7)-C7)</f>
         <v/>
       </c>
       <c r="E7" s="17">
@@ -9225,7 +9225,7 @@
         <v>2054907.91</v>
       </c>
       <c r="D8" s="6">
-        <f>IFERROR(B8-C8,"")</f>
+        <f>IF(C8="","",IF(B8="",0,B8)-C8)</f>
         <v/>
       </c>
       <c r="E8" s="17">
@@ -9248,7 +9248,7 @@
         <v>4111751.01</v>
       </c>
       <c r="D9" s="6">
-        <f>IFERROR(B9-C9,"")</f>
+        <f>IF(C9="","",IF(B9="",0,B9)-C9)</f>
         <v/>
       </c>
       <c r="E9" s="17">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C10" s="17" t="n"/>
       <c r="D10" s="6">
-        <f>IFERROR(B10-C10,"")</f>
+        <f>IF(C10="","",IF(B10="",0,B10)-C10)</f>
         <v/>
       </c>
       <c r="E10" s="17">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="C11" s="17" t="n"/>
       <c r="D11" s="6">
-        <f>IFERROR(B11-C11,"")</f>
+        <f>IF(C11="","",IF(B11="",0,B11)-C11)</f>
         <v/>
       </c>
       <c r="E11" s="17">
@@ -9321,7 +9321,7 @@
         <v>337165.1</v>
       </c>
       <c r="D12" s="6">
-        <f>IFERROR(B12-C12,"")</f>
+        <f>IF(C12="","",IF(B12="",0,B12)-C12)</f>
         <v/>
       </c>
       <c r="E12" s="17">

--- a/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
+++ b/public/downloads/underwriting-demo/sample-t12-analysis.xlsx
@@ -546,7 +546,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>505 West — as of 2026-08-31</t>
+          <t>Sample Mesa Apt — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>505 West — as of 2026-08-31</t>
+          <t>Sample Mesa Apt — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>505 West — as of 2026-08-31</t>
+          <t>Sample Mesa Apt — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -10673,7 +10673,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>505 West — as of 2026-08-31</t>
+          <t>Sample Mesa Apt — as of 2026-08-31</t>
         </is>
       </c>
     </row>
